--- a/tmk/historico_cambios_TMK.xlsx
+++ b/tmk/historico_cambios_TMK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/02 Febrero/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DDC35D9-D645-40B6-B7D9-E184D1DA433F}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91773293-7CD1-4FD6-AD8A-CD863D9EE51B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="44">
   <si>
     <t>Año</t>
   </si>
@@ -125,6 +125,33 @@
   </si>
   <si>
     <t>90%</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>113.3%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
+    <t>104.0%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>116.0%</t>
+  </si>
+  <si>
+    <t>68.0%</t>
+  </si>
+  <si>
+    <t>122.0%</t>
+  </si>
+  <si>
+    <t>96.0%</t>
   </si>
 </sst>
 </file>
@@ -132,7 +159,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -188,7 +215,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
@@ -564,7 +591,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -599,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="K3" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -634,7 +661,7 @@
         <v>17</v>
       </c>
       <c r="K4" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -669,7 +696,7 @@
         <v>17</v>
       </c>
       <c r="K5" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -704,7 +731,7 @@
         <v>17</v>
       </c>
       <c r="K6" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -739,7 +766,7 @@
         <v>17</v>
       </c>
       <c r="K7" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -774,7 +801,7 @@
         <v>17</v>
       </c>
       <c r="K8" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -809,7 +836,7 @@
         <v>17</v>
       </c>
       <c r="K9" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -844,7 +871,7 @@
         <v>17</v>
       </c>
       <c r="K10" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -879,7 +906,357 @@
         <v>17</v>
       </c>
       <c r="K11" s="2">
-        <v>46070.812099905103</v>
+        <v>46070.812099907409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2026</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2026</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
+        <v>58</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2026</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
+      </c>
+      <c r="G18">
+        <v>60.5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2026</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19">
+        <v>150</v>
+      </c>
+      <c r="G19">
+        <v>170</v>
+      </c>
+      <c r="H19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="2">
+        <v>46099.788829440811</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21">
+        <v>100000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="2">
+        <v>46099.788829440811</v>
       </c>
     </row>
   </sheetData>
